--- a/samples/AUMA-blok-rule.xlsx
+++ b/samples/AUMA-blok-rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\На сайт-приложение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29714787-5FA5-4E36-9770-991381057023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7BF087-906D-483C-8B50-12B60FA4E99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7810" yWindow="740" windowWidth="27020" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="1220" windowWidth="21930" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -65,9 +65,6 @@
     <t>{{Explosion protection}}</t>
   </si>
   <si>
-    <t>{{Order}}</t>
-  </si>
-  <si>
     <t>Колонка из .htm</t>
   </si>
   <si>
@@ -126,18 +123,29 @@
   </si>
   <si>
     <t>Паспорт привода в blok-passport-2.pdf</t>
+  </si>
+  <si>
+    <t>{{Article}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -217,16 +225,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -543,21 +552,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -568,25 +577,25 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4"/>
       <c r="D4" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -600,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -614,7 +623,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -628,63 +637,63 @@
         <v>2</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/samples/AUMA-blok-rule.xlsx
+++ b/samples/AUMA-blok-rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\На сайт-приложение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7BF087-906D-483C-8B50-12B60FA4E99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82014BDF-9337-443E-A98B-DE44B7F7F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="1220" windowWidth="21930" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="660" windowWidth="21930" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>только 8 цифрт, без других символов.</t>
   </si>
@@ -80,9 +80,6 @@
     <t>{{Type}}</t>
   </si>
   <si>
-    <t>вместо тире, пробел. (Пример - SAEX 10.2)</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>Interface</t>
   </si>
   <si>
-    <t>{{Temperature version}}</t>
-  </si>
-  <si>
     <t>Temperature version</t>
   </si>
   <si>
@@ -125,7 +119,22 @@
     <t>Паспорт привода в blok-passport-2.pdf</t>
   </si>
   <si>
-    <t>{{Article}}</t>
+    <t>{{Order}}</t>
+  </si>
+  <si>
+    <t>вместо тире, пробел. (Пример - ACEXC 01.2)</t>
+  </si>
+  <si>
+    <t>{{t1}}</t>
+  </si>
+  <si>
+    <t>{{t2}}</t>
+  </si>
+  <si>
+    <t>1,2 цифра</t>
+  </si>
+  <si>
+    <t>3,4 цифра</t>
   </si>
 </sst>
 </file>
@@ -540,19 +549,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65304B45-4765-4EC2-9047-ACADC1B45237}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.36328125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="65.90625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="18.6328125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="127.26953125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="77.36328125" style="3" customWidth="1"/>
     <col min="5" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>13</v>
@@ -564,14 +573,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -580,22 +589,22 @@
         <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
+      <c r="D3" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4"/>
       <c r="D4" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -609,7 +618,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -637,43 +646,43 @@
         <v>2</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>22</v>
+      <c r="A8" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
+      <c r="D8" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="B10" s="7" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2</v>
@@ -684,15 +693,29 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>11</v>
       </c>
     </row>

--- a/samples/AUMA-blok-rule.xlsx
+++ b/samples/AUMA-blok-rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\На сайт-приложение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82014BDF-9337-443E-A98B-DE44B7F7F8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F5541B-805F-4F44-9094-39CD2C9BA4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="660" windowWidth="21930" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5090" yWindow="620" windowWidth="29520" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -83,9 +83,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Terminal plan TPC</t>
-  </si>
-  <si>
     <t>{{Terminal plan TPC}}</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>полное значение, если дынных "Explosion protection" нет, то ничего не вставляется и удалятеся "EAЭC RU С-DЕ.МЕ92.В.00095/19"</t>
   </si>
   <si>
-    <t>Ex electrical connection или Electrical connect. Или WP electrical connection</t>
-  </si>
-  <si>
     <t>Паспорт привода в blok-passport-2.pdf</t>
   </si>
   <si>
@@ -135,18 +129,32 @@
   </si>
   <si>
     <t>3,4 цифра</t>
+  </si>
+  <si>
+    <t>"Ex electrical connection" или "Electrical connect." или "WP electrical connection"</t>
+  </si>
+  <si>
+    <t>"Terminal plan TPC" или "Wiring diagram MSP"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,16 +242,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -553,7 +562,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.36328125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="26.81640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="141.08984375" style="3" customWidth="1"/>
     <col min="3" max="3" width="18.6328125" style="3" customWidth="1"/>
     <col min="4" max="4" width="77.36328125" style="3" customWidth="1"/>
     <col min="5" max="16384" width="8.7265625" style="3"/>
@@ -561,7 +570,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>13</v>
@@ -575,7 +584,7 @@
     </row>
     <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1</v>
@@ -595,16 +604,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4"/>
       <c r="D4" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -618,7 +627,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -646,43 +655,43 @@
         <v>2</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="7" t="s">
         <v>16</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>2</v>
@@ -693,10 +702,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>2</v>
@@ -707,10 +716,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>3</v>

--- a/samples/AUMA-blok-rule.xlsx
+++ b/samples/AUMA-blok-rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\На сайт-приложение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F5541B-805F-4F44-9094-39CD2C9BA4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643BF9E6-E030-49CB-A477-290590C11AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5090" yWindow="620" windowWidth="29520" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5930" yWindow="500" windowWidth="29520" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>только 8 цифрт, без других символов.</t>
   </si>
@@ -77,12 +77,6 @@
     <t>первая колонка из .htm</t>
   </si>
   <si>
-    <t>{{Type}}</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>{{Terminal plan TPC}}</t>
   </si>
   <si>
@@ -135,18 +129,46 @@
   </si>
   <si>
     <t>"Terminal plan TPC" или "Wiring diagram MSP"</t>
+  </si>
+  <si>
+    <t>{{Article}}</t>
+  </si>
+  <si>
+    <t>"Article" или "article"</t>
+  </si>
+  <si>
+    <t>первое значение</t>
+  </si>
+  <si>
+    <t>{{Article2}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="12" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -242,16 +264,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -558,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65304B45-4765-4EC2-9047-ACADC1B45237}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.36328125" style="3" customWidth="1"/>
@@ -570,7 +594,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>13</v>
@@ -584,7 +608,7 @@
     </row>
     <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1</v>
@@ -594,118 +618,118 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
+      <c r="A3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="D4" s="7" t="s">
+      <c r="A4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>23</v>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>30</v>
+      <c r="A8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>2</v>
@@ -716,15 +740,29 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>11</v>
       </c>
     </row>
